--- a/Resuls.xlsx
+++ b/Resuls.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.6667</v>
+        <v>6.67</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.1111</v>
+        <v>6.11</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3333</v>
+        <v>4.33</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>47.6667</v>
+        <v>47.67</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.6667</v>
+        <v>15.67</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>109.6667</v>
+        <v>109.67</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.3333</v>
+        <v>15.33</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>153.3333</v>
+        <v>153.33</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13.1667</v>
+        <v>13.17</v>
       </c>
       <c r="C14" t="n">
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>184.3333</v>
+        <v>184.33</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.1667</v>
+        <v>6.17</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.4444</v>
+        <v>16.44</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>115.1111</v>
+        <v>115.11</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18.1111</v>
+        <v>18.11</v>
       </c>
       <c r="C23" t="n">
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>144.8889</v>
+        <v>144.89</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>30.8889</v>
+        <v>30.89</v>
       </c>
       <c r="C25" t="n">
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>185.3333</v>
+        <v>185.33</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25.6667</v>
+        <v>25.67</v>
       </c>
       <c r="C27" t="n">
         <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>256.6667</v>
+        <v>256.67</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12.5833</v>
+        <v>12.58</v>
       </c>
       <c r="C29" t="n">
         <v>12</v>
